--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_KT.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_KT.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rcccaffd684384852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rcfa8dc84c05f482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Ra617d289b22a41dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R7a386a4da4d74334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rebac24c751564b89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R1b589b01ddc34896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R0ec6b8a9478b4bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R94c3521e9cd34170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R0625dd88b5b9488e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R1568aa940b5343f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Ra1f2f6ebe6a44af2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rdd7a25545c3149e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Re9a6aac9adaf42dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R5be7f05b92234f19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rdc8ef4f44ebe4917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rfd9e5eb90e1b4133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R7c9d034e010c430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R49b8c92772a54fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Ra039910662a74428"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R15734b9e74b749da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R10256274fa914cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rf1a5b28785e14104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rda0d4704e0ab405d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rb7af71910c854a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R33fa16486c704601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R0ae6359be8ac4fd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R8758f61711c840a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R41b638a1f6204c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R7e58046286b44f03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rd9755402f55842aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R414aeee4e84c4484"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R1a9738721cfd4886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R3baf3dac5ce44946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R631f05a99531415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rf4f31f0cf1974e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R36d3fe73947444b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R990d388acc5e434d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R2ff41b487a0a4556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R3bab4eb89057492d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rb1e2989857cb416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R96a3f88131004085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rea3b80b022214d9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Rb5637fc8c04c489f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2813,6 +2814,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>ブルーノ・キャルバート</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・太白派</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
